--- a/DATA/DATA FILES/MARVAIR DATA.xlsx
+++ b/DATA/DATA FILES/MARVAIR DATA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ericc\Documents\HHpro\DATA\DATA FILES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCEA8604-7E88-4331-9353-430DC21CF9E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A12BCAA-4E9C-44FA-BF58-E8F3F98CCB7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{CEC038CA-04AF-4E24-A04D-55CF7AB54A1F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{CEC038CA-04AF-4E24-A04D-55CF7AB54A1F}"/>
   </bookViews>
   <sheets>
     <sheet name="SCHEDULE" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="438" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="439" uniqueCount="110">
   <si>
     <t>CFM</t>
   </si>
@@ -370,6 +370,9 @@
   </si>
   <si>
     <t>7-</t>
+  </si>
+  <si>
+    <t>OPERATION MANUAL</t>
   </si>
 </sst>
 </file>
@@ -756,7 +759,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -827,33 +830,6 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -866,13 +842,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
@@ -881,7 +851,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
@@ -892,6 +862,33 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1265,131 +1262,135 @@
     <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="36" max="36" width="14.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="37" max="37" width="20" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="38" max="38" width="19.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="40" t="s">
         <v>84</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
-      <c r="H1" s="27"/>
-      <c r="I1" s="27"/>
-      <c r="J1" s="27"/>
-      <c r="K1" s="27"/>
-      <c r="L1" s="27"/>
-      <c r="M1" s="27"/>
-      <c r="N1" s="27"/>
-      <c r="O1" s="28"/>
-      <c r="Q1" s="29" t="s">
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
+      <c r="I1" s="41"/>
+      <c r="J1" s="41"/>
+      <c r="K1" s="41"/>
+      <c r="L1" s="41"/>
+      <c r="M1" s="41"/>
+      <c r="N1" s="41"/>
+      <c r="O1" s="42"/>
+      <c r="Q1" s="37" t="s">
         <v>73</v>
       </c>
-      <c r="R1" s="30"/>
-      <c r="S1" s="31"/>
-      <c r="U1" s="26" t="s">
+      <c r="R1" s="38"/>
+      <c r="S1" s="39"/>
+      <c r="U1" s="40" t="s">
         <v>77</v>
       </c>
-      <c r="V1" s="27"/>
-      <c r="W1" s="27"/>
-      <c r="X1" s="27"/>
-      <c r="Y1" s="27"/>
-      <c r="Z1" s="27"/>
-      <c r="AA1" s="27"/>
-      <c r="AB1" s="27"/>
-      <c r="AC1" s="27"/>
-      <c r="AD1" s="27"/>
-      <c r="AE1" s="27"/>
-      <c r="AF1" s="27"/>
-      <c r="AG1" s="27"/>
-      <c r="AH1" s="27"/>
-      <c r="AI1" s="27"/>
-      <c r="AJ1" s="27"/>
-      <c r="AK1" s="28"/>
+      <c r="V1" s="41"/>
+      <c r="W1" s="41"/>
+      <c r="X1" s="41"/>
+      <c r="Y1" s="41"/>
+      <c r="Z1" s="41"/>
+      <c r="AA1" s="41"/>
+      <c r="AB1" s="41"/>
+      <c r="AC1" s="41"/>
+      <c r="AD1" s="41"/>
+      <c r="AE1" s="41"/>
+      <c r="AF1" s="41"/>
+      <c r="AG1" s="41"/>
+      <c r="AH1" s="41"/>
+      <c r="AI1" s="41"/>
+      <c r="AJ1" s="41"/>
+      <c r="AK1" s="41"/>
+      <c r="AL1" s="42"/>
     </row>
     <row r="2" spans="1:38" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="40" t="s">
         <v>80</v>
       </c>
-      <c r="B2" s="27"/>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
-      <c r="G2" s="27"/>
-      <c r="H2" s="27"/>
-      <c r="I2" s="27"/>
-      <c r="J2" s="27"/>
-      <c r="K2" s="27"/>
-      <c r="L2" s="27"/>
-      <c r="M2" s="27"/>
-      <c r="N2" s="27"/>
-      <c r="O2" s="28"/>
-      <c r="Q2" s="24" t="s">
+      <c r="B2" s="41"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
+      <c r="G2" s="41"/>
+      <c r="H2" s="41"/>
+      <c r="I2" s="41"/>
+      <c r="J2" s="41"/>
+      <c r="K2" s="41"/>
+      <c r="L2" s="41"/>
+      <c r="M2" s="41"/>
+      <c r="N2" s="41"/>
+      <c r="O2" s="42"/>
+      <c r="Q2" s="35" t="s">
         <v>74</v>
       </c>
-      <c r="R2" s="24" t="s">
+      <c r="R2" s="35" t="s">
         <v>76</v>
       </c>
-      <c r="S2" s="24" t="s">
+      <c r="S2" s="35" t="s">
         <v>75</v>
       </c>
-      <c r="U2" s="24" t="s">
+      <c r="U2" s="35" t="s">
         <v>85</v>
       </c>
-      <c r="V2" s="24" t="s">
+      <c r="V2" s="35" t="s">
         <v>86</v>
       </c>
-      <c r="W2" s="24" t="s">
+      <c r="W2" s="35" t="s">
         <v>87</v>
       </c>
-      <c r="X2" s="24" t="s">
+      <c r="X2" s="35" t="s">
         <v>88</v>
       </c>
-      <c r="Y2" s="24" t="s">
+      <c r="Y2" s="35" t="s">
         <v>89</v>
       </c>
-      <c r="Z2" s="24" t="s">
+      <c r="Z2" s="35" t="s">
         <v>90</v>
       </c>
-      <c r="AA2" s="24" t="s">
+      <c r="AA2" s="35" t="s">
         <v>91</v>
       </c>
-      <c r="AB2" s="24" t="s">
+      <c r="AB2" s="35" t="s">
         <v>92</v>
       </c>
-      <c r="AC2" s="24" t="s">
+      <c r="AC2" s="35" t="s">
         <v>93</v>
       </c>
-      <c r="AD2" s="24" t="s">
+      <c r="AD2" s="35" t="s">
         <v>94</v>
       </c>
-      <c r="AE2" s="24" t="s">
+      <c r="AE2" s="35" t="s">
         <v>95</v>
       </c>
-      <c r="AF2" s="24" t="s">
+      <c r="AF2" s="35" t="s">
         <v>96</v>
       </c>
-      <c r="AG2" s="24" t="s">
+      <c r="AG2" s="35" t="s">
         <v>97</v>
       </c>
-      <c r="AH2" s="24" t="s">
+      <c r="AH2" s="35" t="s">
         <v>98</v>
       </c>
-      <c r="AI2" s="24" t="s">
+      <c r="AI2" s="35" t="s">
         <v>99</v>
       </c>
-      <c r="AJ2" s="24" t="s">
+      <c r="AJ2" s="35" t="s">
         <v>100</v>
       </c>
-      <c r="AK2" s="24" t="s">
+      <c r="AK2" s="35" t="s">
         <v>101</v>
       </c>
-      <c r="AL2"/>
+      <c r="AL2" s="35" t="s">
+        <v>109</v>
+      </c>
     </row>
     <row r="3" spans="1:38" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
@@ -1437,27 +1438,27 @@
       <c r="O3" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="Q3" s="32"/>
-      <c r="R3" s="32"/>
-      <c r="S3" s="32"/>
-      <c r="U3" s="25"/>
-      <c r="V3" s="25"/>
-      <c r="W3" s="25"/>
-      <c r="X3" s="25"/>
-      <c r="Y3" s="25"/>
-      <c r="Z3" s="25"/>
-      <c r="AA3" s="25"/>
-      <c r="AB3" s="25"/>
-      <c r="AC3" s="25"/>
-      <c r="AD3" s="25"/>
-      <c r="AE3" s="25"/>
-      <c r="AF3" s="25"/>
-      <c r="AG3" s="25"/>
-      <c r="AH3" s="25"/>
-      <c r="AI3" s="25"/>
-      <c r="AJ3" s="25"/>
-      <c r="AK3" s="25"/>
-      <c r="AL3"/>
+      <c r="Q3" s="43"/>
+      <c r="R3" s="43"/>
+      <c r="S3" s="43"/>
+      <c r="U3" s="36"/>
+      <c r="V3" s="36"/>
+      <c r="W3" s="36"/>
+      <c r="X3" s="36"/>
+      <c r="Y3" s="36"/>
+      <c r="Z3" s="36"/>
+      <c r="AA3" s="36"/>
+      <c r="AB3" s="36"/>
+      <c r="AC3" s="36"/>
+      <c r="AD3" s="36"/>
+      <c r="AE3" s="36"/>
+      <c r="AF3" s="36"/>
+      <c r="AG3" s="36"/>
+      <c r="AH3" s="36"/>
+      <c r="AI3" s="36"/>
+      <c r="AJ3" s="36"/>
+      <c r="AK3" s="36"/>
+      <c r="AL3" s="36"/>
     </row>
     <row r="4" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
@@ -1534,7 +1535,8 @@
       <c r="AH4" s="5"/>
       <c r="AI4" s="5"/>
       <c r="AJ4" s="5"/>
-      <c r="AK4" s="6"/>
+      <c r="AK4" s="5"/>
+      <c r="AL4" s="6"/>
     </row>
     <row r="5" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
@@ -1611,7 +1613,8 @@
       <c r="AH5" s="8"/>
       <c r="AI5" s="8"/>
       <c r="AJ5" s="8"/>
-      <c r="AK5" s="9"/>
+      <c r="AK5" s="8"/>
+      <c r="AL5" s="9"/>
     </row>
     <row r="6" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
@@ -1688,7 +1691,8 @@
       <c r="AH6" s="8"/>
       <c r="AI6" s="8"/>
       <c r="AJ6" s="8"/>
-      <c r="AK6" s="9"/>
+      <c r="AK6" s="8"/>
+      <c r="AL6" s="9"/>
     </row>
     <row r="7" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
@@ -1765,7 +1769,8 @@
       <c r="AH7" s="8"/>
       <c r="AI7" s="8"/>
       <c r="AJ7" s="8"/>
-      <c r="AK7" s="9"/>
+      <c r="AK7" s="8"/>
+      <c r="AL7" s="9"/>
     </row>
     <row r="8" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
@@ -1842,7 +1847,8 @@
       <c r="AH8" s="8"/>
       <c r="AI8" s="8"/>
       <c r="AJ8" s="8"/>
-      <c r="AK8" s="9"/>
+      <c r="AK8" s="8"/>
+      <c r="AL8" s="9"/>
     </row>
     <row r="9" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
@@ -1919,7 +1925,8 @@
       <c r="AH9" s="8"/>
       <c r="AI9" s="8"/>
       <c r="AJ9" s="8"/>
-      <c r="AK9" s="9"/>
+      <c r="AK9" s="8"/>
+      <c r="AL9" s="9"/>
     </row>
     <row r="10" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
@@ -1996,7 +2003,8 @@
       <c r="AH10" s="8"/>
       <c r="AI10" s="8"/>
       <c r="AJ10" s="8"/>
-      <c r="AK10" s="9"/>
+      <c r="AK10" s="8"/>
+      <c r="AL10" s="9"/>
     </row>
     <row r="11" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
@@ -2073,7 +2081,8 @@
       <c r="AH11" s="8"/>
       <c r="AI11" s="8"/>
       <c r="AJ11" s="8"/>
-      <c r="AK11" s="9"/>
+      <c r="AK11" s="8"/>
+      <c r="AL11" s="9"/>
     </row>
     <row r="12" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
@@ -2150,7 +2159,8 @@
       <c r="AH12" s="8"/>
       <c r="AI12" s="8"/>
       <c r="AJ12" s="8"/>
-      <c r="AK12" s="9"/>
+      <c r="AK12" s="8"/>
+      <c r="AL12" s="9"/>
     </row>
     <row r="13" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
@@ -2227,7 +2237,8 @@
       <c r="AH13" s="8"/>
       <c r="AI13" s="8"/>
       <c r="AJ13" s="8"/>
-      <c r="AK13" s="9"/>
+      <c r="AK13" s="8"/>
+      <c r="AL13" s="9"/>
     </row>
     <row r="14" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
@@ -2304,7 +2315,8 @@
       <c r="AH14" s="8"/>
       <c r="AI14" s="8"/>
       <c r="AJ14" s="8"/>
-      <c r="AK14" s="9"/>
+      <c r="AK14" s="8"/>
+      <c r="AL14" s="9"/>
     </row>
     <row r="15" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
@@ -2381,7 +2393,8 @@
       <c r="AH15" s="8"/>
       <c r="AI15" s="8"/>
       <c r="AJ15" s="8"/>
-      <c r="AK15" s="9"/>
+      <c r="AK15" s="8"/>
+      <c r="AL15" s="9"/>
     </row>
     <row r="16" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
@@ -2458,9 +2471,10 @@
       <c r="AH16" s="8"/>
       <c r="AI16" s="8"/>
       <c r="AJ16" s="8"/>
-      <c r="AK16" s="9"/>
-    </row>
-    <row r="17" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK16" s="8"/>
+      <c r="AL16" s="9"/>
+    </row>
+    <row r="17" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
         <v>82</v>
       </c>
@@ -2535,9 +2549,10 @@
       <c r="AH17" s="8"/>
       <c r="AI17" s="8"/>
       <c r="AJ17" s="8"/>
-      <c r="AK17" s="9"/>
-    </row>
-    <row r="18" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK17" s="8"/>
+      <c r="AL17" s="9"/>
+    </row>
+    <row r="18" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
         <v>82</v>
       </c>
@@ -2612,9 +2627,10 @@
       <c r="AH18" s="8"/>
       <c r="AI18" s="8"/>
       <c r="AJ18" s="8"/>
-      <c r="AK18" s="9"/>
-    </row>
-    <row r="19" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK18" s="8"/>
+      <c r="AL18" s="9"/>
+    </row>
+    <row r="19" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
         <v>82</v>
       </c>
@@ -2689,9 +2705,10 @@
       <c r="AH19" s="8"/>
       <c r="AI19" s="8"/>
       <c r="AJ19" s="8"/>
-      <c r="AK19" s="9"/>
-    </row>
-    <row r="20" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK19" s="8"/>
+      <c r="AL19" s="9"/>
+    </row>
+    <row r="20" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
         <v>82</v>
       </c>
@@ -2766,9 +2783,10 @@
       <c r="AH20" s="8"/>
       <c r="AI20" s="8"/>
       <c r="AJ20" s="8"/>
-      <c r="AK20" s="9"/>
-    </row>
-    <row r="21" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK20" s="8"/>
+      <c r="AL20" s="9"/>
+    </row>
+    <row r="21" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
         <v>82</v>
       </c>
@@ -2843,9 +2861,10 @@
       <c r="AH21" s="8"/>
       <c r="AI21" s="8"/>
       <c r="AJ21" s="8"/>
-      <c r="AK21" s="9"/>
-    </row>
-    <row r="22" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK21" s="8"/>
+      <c r="AL21" s="9"/>
+    </row>
+    <row r="22" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
         <v>82</v>
       </c>
@@ -2920,9 +2939,10 @@
       <c r="AH22" s="8"/>
       <c r="AI22" s="8"/>
       <c r="AJ22" s="8"/>
-      <c r="AK22" s="9"/>
-    </row>
-    <row r="23" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK22" s="8"/>
+      <c r="AL22" s="9"/>
+    </row>
+    <row r="23" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
         <v>82</v>
       </c>
@@ -2997,9 +3017,10 @@
       <c r="AH23" s="8"/>
       <c r="AI23" s="8"/>
       <c r="AJ23" s="8"/>
-      <c r="AK23" s="9"/>
-    </row>
-    <row r="24" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK23" s="8"/>
+      <c r="AL23" s="9"/>
+    </row>
+    <row r="24" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
         <v>82</v>
       </c>
@@ -3074,9 +3095,10 @@
       <c r="AH24" s="8"/>
       <c r="AI24" s="8"/>
       <c r="AJ24" s="8"/>
-      <c r="AK24" s="9"/>
-    </row>
-    <row r="25" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK24" s="8"/>
+      <c r="AL24" s="9"/>
+    </row>
+    <row r="25" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
         <v>82</v>
       </c>
@@ -3151,9 +3173,10 @@
       <c r="AH25" s="8"/>
       <c r="AI25" s="8"/>
       <c r="AJ25" s="8"/>
-      <c r="AK25" s="9"/>
-    </row>
-    <row r="26" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK25" s="8"/>
+      <c r="AL25" s="9"/>
+    </row>
+    <row r="26" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
         <v>82</v>
       </c>
@@ -3228,9 +3251,10 @@
       <c r="AH26" s="8"/>
       <c r="AI26" s="8"/>
       <c r="AJ26" s="8"/>
-      <c r="AK26" s="9"/>
-    </row>
-    <row r="27" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK26" s="8"/>
+      <c r="AL26" s="9"/>
+    </row>
+    <row r="27" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
         <v>82</v>
       </c>
@@ -3305,9 +3329,10 @@
       <c r="AH27" s="8"/>
       <c r="AI27" s="8"/>
       <c r="AJ27" s="8"/>
-      <c r="AK27" s="9"/>
-    </row>
-    <row r="28" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK27" s="8"/>
+      <c r="AL27" s="9"/>
+    </row>
+    <row r="28" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
         <v>82</v>
       </c>
@@ -3382,9 +3407,10 @@
       <c r="AH28" s="8"/>
       <c r="AI28" s="8"/>
       <c r="AJ28" s="8"/>
-      <c r="AK28" s="9"/>
-    </row>
-    <row r="29" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK28" s="8"/>
+      <c r="AL28" s="9"/>
+    </row>
+    <row r="29" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
         <v>82</v>
       </c>
@@ -3459,9 +3485,10 @@
       <c r="AH29" s="8"/>
       <c r="AI29" s="8"/>
       <c r="AJ29" s="8"/>
-      <c r="AK29" s="9"/>
-    </row>
-    <row r="30" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK29" s="8"/>
+      <c r="AL29" s="9"/>
+    </row>
+    <row r="30" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
         <v>82</v>
       </c>
@@ -3536,9 +3563,10 @@
       <c r="AH30" s="8"/>
       <c r="AI30" s="8"/>
       <c r="AJ30" s="8"/>
-      <c r="AK30" s="9"/>
-    </row>
-    <row r="31" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK30" s="8"/>
+      <c r="AL30" s="9"/>
+    </row>
+    <row r="31" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
         <v>82</v>
       </c>
@@ -3613,9 +3641,10 @@
       <c r="AH31" s="8"/>
       <c r="AI31" s="8"/>
       <c r="AJ31" s="8"/>
-      <c r="AK31" s="9"/>
-    </row>
-    <row r="32" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK31" s="8"/>
+      <c r="AL31" s="9"/>
+    </row>
+    <row r="32" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
         <v>82</v>
       </c>
@@ -3690,9 +3719,10 @@
       <c r="AH32" s="8"/>
       <c r="AI32" s="8"/>
       <c r="AJ32" s="8"/>
-      <c r="AK32" s="9"/>
-    </row>
-    <row r="33" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK32" s="8"/>
+      <c r="AL32" s="9"/>
+    </row>
+    <row r="33" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
         <v>82</v>
       </c>
@@ -3767,9 +3797,10 @@
       <c r="AH33" s="8"/>
       <c r="AI33" s="8"/>
       <c r="AJ33" s="8"/>
-      <c r="AK33" s="9"/>
-    </row>
-    <row r="34" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK33" s="8"/>
+      <c r="AL33" s="9"/>
+    </row>
+    <row r="34" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="s">
         <v>82</v>
       </c>
@@ -3844,9 +3875,10 @@
       <c r="AH34" s="8"/>
       <c r="AI34" s="8"/>
       <c r="AJ34" s="8"/>
-      <c r="AK34" s="9"/>
-    </row>
-    <row r="35" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK34" s="8"/>
+      <c r="AL34" s="9"/>
+    </row>
+    <row r="35" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
         <v>82</v>
       </c>
@@ -3921,9 +3953,10 @@
       <c r="AH35" s="8"/>
       <c r="AI35" s="8"/>
       <c r="AJ35" s="8"/>
-      <c r="AK35" s="9"/>
-    </row>
-    <row r="36" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK35" s="8"/>
+      <c r="AL35" s="9"/>
+    </row>
+    <row r="36" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A36" s="7" t="s">
         <v>82</v>
       </c>
@@ -3998,9 +4031,10 @@
       <c r="AH36" s="8"/>
       <c r="AI36" s="8"/>
       <c r="AJ36" s="8"/>
-      <c r="AK36" s="9"/>
-    </row>
-    <row r="37" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK36" s="8"/>
+      <c r="AL36" s="9"/>
+    </row>
+    <row r="37" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
         <v>82</v>
       </c>
@@ -4075,9 +4109,10 @@
       <c r="AH37" s="8"/>
       <c r="AI37" s="8"/>
       <c r="AJ37" s="8"/>
-      <c r="AK37" s="9"/>
-    </row>
-    <row r="38" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK37" s="8"/>
+      <c r="AL37" s="9"/>
+    </row>
+    <row r="38" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A38" s="7" t="s">
         <v>82</v>
       </c>
@@ -4152,9 +4187,10 @@
       <c r="AH38" s="8"/>
       <c r="AI38" s="8"/>
       <c r="AJ38" s="8"/>
-      <c r="AK38" s="9"/>
-    </row>
-    <row r="39" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK38" s="8"/>
+      <c r="AL38" s="9"/>
+    </row>
+    <row r="39" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
         <v>82</v>
       </c>
@@ -4229,9 +4265,10 @@
       <c r="AH39" s="8"/>
       <c r="AI39" s="8"/>
       <c r="AJ39" s="8"/>
-      <c r="AK39" s="9"/>
-    </row>
-    <row r="40" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK39" s="8"/>
+      <c r="AL39" s="9"/>
+    </row>
+    <row r="40" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A40" s="7" t="s">
         <v>82</v>
       </c>
@@ -4306,9 +4343,10 @@
       <c r="AH40" s="8"/>
       <c r="AI40" s="8"/>
       <c r="AJ40" s="8"/>
-      <c r="AK40" s="9"/>
-    </row>
-    <row r="41" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK40" s="8"/>
+      <c r="AL40" s="9"/>
+    </row>
+    <row r="41" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
         <v>82</v>
       </c>
@@ -4383,9 +4421,10 @@
       <c r="AH41" s="8"/>
       <c r="AI41" s="8"/>
       <c r="AJ41" s="8"/>
-      <c r="AK41" s="9"/>
-    </row>
-    <row r="42" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK41" s="8"/>
+      <c r="AL41" s="9"/>
+    </row>
+    <row r="42" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A42" s="7" t="s">
         <v>82</v>
       </c>
@@ -4460,9 +4499,10 @@
       <c r="AH42" s="8"/>
       <c r="AI42" s="8"/>
       <c r="AJ42" s="8"/>
-      <c r="AK42" s="9"/>
-    </row>
-    <row r="43" spans="1:37" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="AK42" s="8"/>
+      <c r="AL42" s="9"/>
+    </row>
+    <row r="43" spans="1:38" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="15" t="s">
         <v>82</v>
       </c>
@@ -4537,9 +4577,10 @@
       <c r="AH43" s="16"/>
       <c r="AI43" s="16"/>
       <c r="AJ43" s="16"/>
-      <c r="AK43" s="17"/>
-    </row>
-    <row r="44" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK43" s="16"/>
+      <c r="AL43" s="17"/>
+    </row>
+    <row r="44" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A44"/>
       <c r="B44"/>
       <c r="C44"/>
@@ -4557,7 +4598,7 @@
       <c r="O44"/>
       <c r="P44"/>
     </row>
-    <row r="45" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A45"/>
       <c r="B45"/>
       <c r="C45"/>
@@ -4575,7 +4616,7 @@
       <c r="O45"/>
       <c r="P45"/>
     </row>
-    <row r="46" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A46"/>
       <c r="B46"/>
       <c r="C46"/>
@@ -4593,7 +4634,7 @@
       <c r="O46"/>
       <c r="P46"/>
     </row>
-    <row r="47" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A47"/>
       <c r="B47"/>
       <c r="C47"/>
@@ -4614,7 +4655,7 @@
       <c r="R47"/>
       <c r="S47"/>
     </row>
-    <row r="48" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A48"/>
       <c r="B48"/>
       <c r="C48"/>
@@ -5182,17 +5223,10 @@
       <c r="M1048570" s="8"/>
     </row>
   </sheetData>
-  <mergeCells count="24">
-    <mergeCell ref="Z2:Z3"/>
-    <mergeCell ref="Q1:S1"/>
-    <mergeCell ref="A2:O2"/>
-    <mergeCell ref="A1:O1"/>
-    <mergeCell ref="Q2:Q3"/>
-    <mergeCell ref="R2:R3"/>
-    <mergeCell ref="S2:S3"/>
-    <mergeCell ref="U2:U3"/>
+  <mergeCells count="25">
+    <mergeCell ref="AL2:AL3"/>
+    <mergeCell ref="U1:AL1"/>
     <mergeCell ref="AK2:AK3"/>
-    <mergeCell ref="U1:AK1"/>
     <mergeCell ref="AF2:AF3"/>
     <mergeCell ref="AG2:AG3"/>
     <mergeCell ref="AH2:AH3"/>
@@ -5207,6 +5241,14 @@
     <mergeCell ref="W2:W3"/>
     <mergeCell ref="X2:X3"/>
     <mergeCell ref="Y2:Y3"/>
+    <mergeCell ref="Z2:Z3"/>
+    <mergeCell ref="Q1:S1"/>
+    <mergeCell ref="A2:O2"/>
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="Q2:Q3"/>
+    <mergeCell ref="R2:R3"/>
+    <mergeCell ref="S2:S3"/>
+    <mergeCell ref="U2:U3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5224,742 +5266,459 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="24" t="s">
         <v>102</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
-      <c r="I1" s="34"/>
-      <c r="J1" s="34"/>
-      <c r="K1" s="34"/>
-      <c r="L1" s="34"/>
-      <c r="M1" s="34"/>
-      <c r="N1" s="34"/>
-      <c r="O1" s="35"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
+      <c r="I1" s="25"/>
+      <c r="J1" s="25"/>
+      <c r="K1" s="25"/>
+      <c r="L1" s="25"/>
+      <c r="M1" s="25"/>
+      <c r="N1" s="25"/>
+      <c r="O1" s="26"/>
     </row>
     <row r="2" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="36" t="s">
+      <c r="A2" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="37" t="s">
+      <c r="B2" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="C2" s="37"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
-      <c r="G2" s="39" t="s">
+      <c r="C2" s="11"/>
+      <c r="G2" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="H2" s="37" t="s">
+      <c r="H2" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="I2" s="37"/>
-      <c r="J2" s="37"/>
-      <c r="K2" s="38"/>
-      <c r="L2" s="38"/>
-      <c r="M2" s="38"/>
-      <c r="N2" s="38"/>
-      <c r="O2" s="40"/>
+      <c r="I2" s="11"/>
+      <c r="J2" s="11"/>
+      <c r="O2" s="29"/>
     </row>
     <row r="3" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="36" t="s">
+      <c r="A3" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="37" t="s">
+      <c r="B3" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="C3" s="37"/>
-      <c r="D3" s="38"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="38"/>
-      <c r="G3" s="39" t="s">
+      <c r="C3" s="11"/>
+      <c r="G3" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="H3" s="37" t="s">
+      <c r="H3" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="I3" s="37"/>
-      <c r="J3" s="37"/>
-      <c r="K3" s="38"/>
-      <c r="L3" s="38"/>
-      <c r="M3" s="38"/>
-      <c r="N3" s="38"/>
-      <c r="O3" s="40"/>
+      <c r="I3" s="11"/>
+      <c r="J3" s="11"/>
+      <c r="O3" s="29"/>
     </row>
     <row r="4" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="36" t="s">
+      <c r="A4" s="27" t="s">
         <v>104</v>
       </c>
-      <c r="B4" s="37" t="s">
+      <c r="B4" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="37"/>
-      <c r="D4" s="38"/>
-      <c r="E4" s="38"/>
-      <c r="F4" s="38"/>
-      <c r="G4" s="39" t="s">
+      <c r="C4" s="11"/>
+      <c r="G4" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="H4" s="37" t="s">
+      <c r="H4" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="I4" s="37"/>
-      <c r="J4" s="37"/>
-      <c r="K4" s="38"/>
-      <c r="L4" s="38"/>
-      <c r="M4" s="38"/>
-      <c r="N4" s="38"/>
-      <c r="O4" s="40"/>
+      <c r="I4" s="11"/>
+      <c r="J4" s="11"/>
+      <c r="O4" s="29"/>
       <c r="Q4"/>
       <c r="R4"/>
       <c r="S4"/>
     </row>
     <row r="5" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="36" t="s">
+      <c r="A5" s="27" t="s">
         <v>105</v>
       </c>
-      <c r="B5" s="37" t="s">
+      <c r="B5" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="37"/>
-      <c r="D5" s="38"/>
-      <c r="E5" s="38"/>
-      <c r="F5" s="38"/>
-      <c r="G5" s="39" t="s">
+      <c r="C5" s="11"/>
+      <c r="G5" s="28" t="s">
         <v>28</v>
       </c>
-      <c r="H5" s="37" t="s">
+      <c r="H5" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="I5" s="37"/>
-      <c r="J5" s="37"/>
-      <c r="K5" s="38"/>
-      <c r="L5" s="38"/>
-      <c r="M5" s="38"/>
-      <c r="N5" s="38"/>
-      <c r="O5" s="40"/>
+      <c r="I5" s="11"/>
+      <c r="J5" s="11"/>
+      <c r="O5" s="29"/>
       <c r="Q5"/>
       <c r="R5"/>
       <c r="S5"/>
     </row>
     <row r="6" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="36" t="s">
+      <c r="A6" s="27" t="s">
         <v>106</v>
       </c>
-      <c r="B6" s="37" t="s">
+      <c r="B6" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="37"/>
-      <c r="D6" s="38"/>
-      <c r="E6" s="38"/>
-      <c r="F6" s="38"/>
-      <c r="G6" s="39" t="s">
+      <c r="C6" s="11"/>
+      <c r="G6" s="28" t="s">
         <v>29</v>
       </c>
-      <c r="H6" s="37" t="s">
+      <c r="H6" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="I6" s="37"/>
-      <c r="J6" s="37"/>
-      <c r="K6" s="38"/>
-      <c r="L6" s="38"/>
-      <c r="M6" s="38"/>
-      <c r="N6" s="38"/>
-      <c r="O6" s="40"/>
+      <c r="I6" s="11"/>
+      <c r="J6" s="11"/>
+      <c r="O6" s="29"/>
       <c r="Q6"/>
       <c r="R6"/>
       <c r="S6"/>
     </row>
     <row r="7" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="36" t="s">
+      <c r="A7" s="27" t="s">
         <v>107</v>
       </c>
-      <c r="B7" s="37" t="s">
+      <c r="B7" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="C7" s="37"/>
-      <c r="D7" s="38"/>
-      <c r="E7" s="38"/>
-      <c r="F7" s="38"/>
-      <c r="G7" s="39" t="s">
+      <c r="C7" s="11"/>
+      <c r="G7" s="28" t="s">
         <v>30</v>
       </c>
-      <c r="H7" s="37" t="s">
+      <c r="H7" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="I7" s="37"/>
-      <c r="J7" s="37"/>
-      <c r="K7" s="38"/>
-      <c r="L7" s="38"/>
-      <c r="M7" s="38"/>
-      <c r="N7" s="38"/>
-      <c r="O7" s="40"/>
+      <c r="I7" s="11"/>
+      <c r="J7" s="11"/>
+      <c r="O7" s="29"/>
       <c r="Q7"/>
       <c r="R7"/>
       <c r="S7"/>
     </row>
     <row r="8" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="36" t="s">
+      <c r="A8" s="27" t="s">
         <v>108</v>
       </c>
-      <c r="B8" s="37" t="s">
+      <c r="B8" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="C8" s="37"/>
-      <c r="D8" s="38"/>
-      <c r="E8" s="38"/>
-      <c r="F8" s="38"/>
-      <c r="G8" s="39" t="s">
+      <c r="C8" s="11"/>
+      <c r="G8" s="28" t="s">
         <v>49</v>
       </c>
-      <c r="H8" s="37" t="s">
+      <c r="H8" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="I8" s="37"/>
-      <c r="J8" s="37"/>
-      <c r="K8" s="38"/>
-      <c r="L8" s="38"/>
-      <c r="M8" s="38"/>
-      <c r="N8" s="38"/>
-      <c r="O8" s="40"/>
+      <c r="I8" s="11"/>
+      <c r="J8" s="11"/>
+      <c r="O8" s="29"/>
       <c r="Q8"/>
       <c r="R8"/>
       <c r="S8"/>
     </row>
     <row r="9" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="41" t="s">
+      <c r="A9" s="30" t="s">
         <v>103</v>
       </c>
-      <c r="B9" s="37"/>
-      <c r="C9" s="37"/>
-      <c r="D9" s="38"/>
-      <c r="E9" s="38"/>
-      <c r="F9" s="38"/>
-      <c r="G9" s="42"/>
-      <c r="H9" s="37"/>
-      <c r="I9" s="37"/>
-      <c r="J9" s="42"/>
-      <c r="K9" s="37"/>
-      <c r="L9" s="38"/>
-      <c r="M9" s="38"/>
-      <c r="N9" s="38"/>
-      <c r="O9" s="40"/>
+      <c r="B9" s="11"/>
+      <c r="C9" s="11"/>
+      <c r="G9" s="31"/>
+      <c r="H9" s="11"/>
+      <c r="I9" s="11"/>
+      <c r="J9" s="31"/>
+      <c r="K9" s="11"/>
+      <c r="O9" s="29"/>
       <c r="Q9"/>
       <c r="R9"/>
       <c r="S9"/>
     </row>
     <row r="10" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="36" t="s">
+      <c r="A10" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="37" t="s">
+      <c r="B10" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="C10" s="37"/>
-      <c r="D10" s="38"/>
-      <c r="E10" s="38"/>
-      <c r="F10" s="38"/>
-      <c r="G10" s="39"/>
-      <c r="H10" s="37"/>
-      <c r="I10" s="37"/>
-      <c r="J10" s="42" t="s">
+      <c r="C10" s="11"/>
+      <c r="G10" s="28"/>
+      <c r="H10" s="11"/>
+      <c r="I10" s="11"/>
+      <c r="J10" s="31" t="s">
         <v>56</v>
       </c>
-      <c r="K10" s="37"/>
-      <c r="L10" s="38"/>
-      <c r="M10" s="38"/>
-      <c r="N10" s="38"/>
-      <c r="O10" s="40"/>
+      <c r="K10" s="11"/>
+      <c r="O10" s="29"/>
       <c r="Q10"/>
       <c r="R10"/>
       <c r="S10"/>
     </row>
     <row r="11" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="36" t="s">
+      <c r="A11" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="37" t="s">
+      <c r="B11" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="C11" s="37"/>
-      <c r="D11" s="38"/>
-      <c r="E11" s="38"/>
-      <c r="F11" s="38"/>
-      <c r="G11" s="39"/>
-      <c r="H11" s="37"/>
-      <c r="I11" s="37"/>
-      <c r="J11" s="39" t="s">
+      <c r="C11" s="11"/>
+      <c r="G11" s="28"/>
+      <c r="H11" s="11"/>
+      <c r="I11" s="11"/>
+      <c r="J11" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="K11" s="37" t="s">
+      <c r="K11" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="L11" s="38"/>
-      <c r="M11" s="38"/>
-      <c r="N11" s="38"/>
-      <c r="O11" s="40"/>
+      <c r="O11" s="29"/>
       <c r="Q11"/>
       <c r="R11"/>
       <c r="S11"/>
     </row>
     <row r="12" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="36" t="s">
+      <c r="A12" s="27" t="s">
         <v>104</v>
       </c>
-      <c r="B12" s="37" t="s">
+      <c r="B12" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="C12" s="37"/>
-      <c r="D12" s="38"/>
-      <c r="E12" s="38"/>
-      <c r="F12" s="38"/>
-      <c r="G12" s="39"/>
-      <c r="H12" s="37"/>
-      <c r="I12" s="37"/>
-      <c r="J12" s="39" t="s">
+      <c r="C12" s="11"/>
+      <c r="G12" s="28"/>
+      <c r="H12" s="11"/>
+      <c r="I12" s="11"/>
+      <c r="J12" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="K12" s="37" t="s">
+      <c r="K12" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="L12" s="38"/>
-      <c r="M12" s="38"/>
-      <c r="N12" s="38"/>
-      <c r="O12" s="40"/>
+      <c r="O12" s="29"/>
       <c r="Q12"/>
       <c r="R12"/>
       <c r="S12"/>
     </row>
     <row r="13" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="36" t="s">
+      <c r="A13" s="27" t="s">
         <v>105</v>
       </c>
-      <c r="B13" s="37" t="s">
+      <c r="B13" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="C13" s="37"/>
-      <c r="D13" s="38"/>
-      <c r="E13" s="38"/>
-      <c r="F13" s="38"/>
-      <c r="G13" s="39"/>
-      <c r="H13" s="37"/>
-      <c r="I13" s="37"/>
-      <c r="J13" s="37"/>
-      <c r="K13" s="38"/>
-      <c r="L13" s="38"/>
-      <c r="M13" s="38"/>
-      <c r="N13" s="38"/>
-      <c r="O13" s="40"/>
+      <c r="C13" s="11"/>
+      <c r="G13" s="28"/>
+      <c r="H13" s="11"/>
+      <c r="I13" s="11"/>
+      <c r="J13" s="11"/>
+      <c r="O13" s="29"/>
       <c r="Q13"/>
       <c r="R13"/>
       <c r="S13"/>
     </row>
     <row r="14" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="36" t="s">
+      <c r="A14" s="27" t="s">
         <v>106</v>
       </c>
-      <c r="B14" s="37" t="s">
+      <c r="B14" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="C14" s="37"/>
-      <c r="D14" s="38"/>
-      <c r="E14" s="38"/>
-      <c r="F14" s="38"/>
-      <c r="G14" s="38"/>
-      <c r="H14" s="39"/>
-      <c r="I14" s="39"/>
-      <c r="J14" s="37"/>
-      <c r="K14" s="38"/>
-      <c r="L14" s="38"/>
-      <c r="M14" s="38"/>
-      <c r="N14" s="38"/>
-      <c r="O14" s="40"/>
+      <c r="C14" s="11"/>
+      <c r="H14" s="28"/>
+      <c r="I14" s="28"/>
+      <c r="J14" s="11"/>
+      <c r="O14" s="29"/>
       <c r="Q14"/>
       <c r="R14"/>
       <c r="S14"/>
     </row>
     <row r="15" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="36"/>
-      <c r="B15" s="37" t="s">
+      <c r="A15" s="27"/>
+      <c r="B15" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="C15" s="37" t="s">
+      <c r="C15" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="D15" s="38"/>
-      <c r="E15" s="38"/>
-      <c r="F15" s="38"/>
-      <c r="G15" s="38"/>
-      <c r="H15" s="39"/>
-      <c r="I15" s="39"/>
-      <c r="J15" s="37"/>
-      <c r="K15" s="38"/>
-      <c r="L15" s="38"/>
-      <c r="M15" s="38"/>
-      <c r="N15" s="38"/>
-      <c r="O15" s="40"/>
+      <c r="H15" s="28"/>
+      <c r="I15" s="28"/>
+      <c r="J15" s="11"/>
+      <c r="O15" s="29"/>
     </row>
     <row r="16" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="36"/>
-      <c r="B16" s="37" t="s">
+      <c r="A16" s="27"/>
+      <c r="B16" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="C16" s="37" t="s">
+      <c r="C16" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="D16" s="38"/>
-      <c r="E16" s="38"/>
-      <c r="F16" s="38"/>
-      <c r="G16" s="38"/>
-      <c r="H16" s="39"/>
-      <c r="I16" s="39"/>
-      <c r="J16" s="37"/>
-      <c r="K16" s="38"/>
-      <c r="L16" s="38"/>
-      <c r="M16" s="38"/>
-      <c r="N16" s="38"/>
-      <c r="O16" s="40"/>
+      <c r="H16" s="28"/>
+      <c r="I16" s="28"/>
+      <c r="J16" s="11"/>
+      <c r="O16" s="29"/>
     </row>
     <row r="17" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="36"/>
-      <c r="B17" s="37" t="s">
+      <c r="A17" s="27"/>
+      <c r="B17" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="C17" s="37" t="s">
+      <c r="C17" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="D17" s="38"/>
-      <c r="E17" s="38"/>
-      <c r="F17" s="38"/>
-      <c r="G17" s="38"/>
-      <c r="H17" s="38"/>
-      <c r="I17" s="38"/>
-      <c r="J17" s="38"/>
-      <c r="K17" s="38"/>
-      <c r="L17" s="38"/>
-      <c r="M17" s="38"/>
-      <c r="N17" s="38"/>
-      <c r="O17" s="40"/>
+      <c r="O17" s="29"/>
     </row>
     <row r="18" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="36"/>
-      <c r="B18" s="37" t="s">
+      <c r="A18" s="27"/>
+      <c r="B18" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="C18" s="37" t="s">
+      <c r="C18" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="D18" s="38"/>
-      <c r="E18" s="38"/>
-      <c r="F18" s="38"/>
-      <c r="G18" s="38"/>
-      <c r="H18" s="38"/>
-      <c r="I18" s="38"/>
-      <c r="J18" s="38"/>
-      <c r="K18" s="38"/>
-      <c r="L18" s="38"/>
-      <c r="M18" s="38"/>
-      <c r="N18" s="38"/>
-      <c r="O18" s="40"/>
+      <c r="O18" s="29"/>
     </row>
     <row r="19" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="36" t="s">
+      <c r="A19" s="27" t="s">
         <v>107</v>
       </c>
-      <c r="B19" s="37" t="s">
+      <c r="B19" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="C19" s="38"/>
-      <c r="D19" s="38"/>
-      <c r="E19" s="38"/>
-      <c r="F19" s="38"/>
-      <c r="G19" s="38"/>
-      <c r="H19" s="38"/>
-      <c r="I19" s="38"/>
-      <c r="J19" s="38"/>
-      <c r="K19" s="38"/>
-      <c r="L19" s="38"/>
-      <c r="M19" s="38"/>
-      <c r="N19" s="38"/>
-      <c r="O19" s="40"/>
+      <c r="O19" s="29"/>
     </row>
     <row r="20" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="36"/>
-      <c r="B20" s="39" t="s">
+      <c r="A20" s="27"/>
+      <c r="B20" s="28" t="s">
         <v>59</v>
       </c>
-      <c r="C20" s="37" t="s">
+      <c r="C20" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="D20" s="38"/>
-      <c r="E20" s="38"/>
-      <c r="F20" s="38"/>
-      <c r="G20" s="38"/>
-      <c r="H20" s="38"/>
-      <c r="I20" s="38"/>
-      <c r="J20" s="38"/>
-      <c r="K20" s="38"/>
-      <c r="L20" s="38"/>
-      <c r="M20" s="38"/>
-      <c r="N20" s="38"/>
-      <c r="O20" s="40"/>
+      <c r="O20" s="29"/>
     </row>
     <row r="21" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="36"/>
-      <c r="B21" s="39" t="s">
+      <c r="A21" s="27"/>
+      <c r="B21" s="28" t="s">
         <v>59</v>
       </c>
-      <c r="C21" s="37" t="s">
+      <c r="C21" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="D21" s="38"/>
-      <c r="E21" s="38"/>
-      <c r="F21" s="38"/>
-      <c r="G21" s="38"/>
-      <c r="H21" s="38"/>
-      <c r="I21" s="38"/>
-      <c r="J21" s="38"/>
-      <c r="K21" s="38"/>
-      <c r="L21" s="38"/>
-      <c r="M21" s="38"/>
-      <c r="N21" s="38"/>
-      <c r="O21" s="40"/>
+      <c r="O21" s="29"/>
     </row>
     <row r="22" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="36"/>
-      <c r="B22" s="39" t="s">
+      <c r="A22" s="27"/>
+      <c r="B22" s="28" t="s">
         <v>59</v>
       </c>
-      <c r="C22" s="37" t="s">
+      <c r="C22" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="D22" s="38"/>
-      <c r="E22" s="38"/>
-      <c r="F22" s="38"/>
-      <c r="G22" s="38"/>
-      <c r="H22" s="38"/>
-      <c r="I22" s="38"/>
-      <c r="J22" s="38"/>
-      <c r="K22" s="38"/>
-      <c r="L22" s="38"/>
-      <c r="M22" s="38"/>
-      <c r="N22" s="38"/>
-      <c r="O22" s="40"/>
+      <c r="O22" s="29"/>
     </row>
     <row r="23" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="36"/>
-      <c r="B23" s="39" t="s">
+      <c r="A23" s="27"/>
+      <c r="B23" s="28" t="s">
         <v>59</v>
       </c>
-      <c r="C23" s="37" t="s">
+      <c r="C23" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="D23" s="38"/>
-      <c r="E23" s="38"/>
-      <c r="F23" s="38"/>
-      <c r="G23" s="38"/>
-      <c r="H23" s="38"/>
-      <c r="I23" s="38"/>
-      <c r="J23" s="38"/>
-      <c r="K23" s="38"/>
-      <c r="L23" s="38"/>
-      <c r="M23" s="38"/>
-      <c r="N23" s="38"/>
-      <c r="O23" s="40"/>
+      <c r="O23" s="29"/>
     </row>
     <row r="24" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="36"/>
-      <c r="B24" s="39" t="s">
+      <c r="A24" s="27"/>
+      <c r="B24" s="28" t="s">
         <v>59</v>
       </c>
-      <c r="C24" s="37" t="s">
+      <c r="C24" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="D24" s="38"/>
-      <c r="E24" s="38"/>
-      <c r="F24" s="38"/>
-      <c r="G24" s="38"/>
-      <c r="H24" s="38"/>
-      <c r="I24" s="38"/>
-      <c r="J24" s="38"/>
-      <c r="K24" s="38"/>
-      <c r="L24" s="38"/>
-      <c r="M24" s="38"/>
-      <c r="N24" s="38"/>
-      <c r="O24" s="40"/>
+      <c r="O24" s="29"/>
     </row>
     <row r="25" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="36" t="s">
+      <c r="A25" s="27" t="s">
         <v>108</v>
       </c>
-      <c r="B25" s="37" t="s">
+      <c r="B25" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="C25" s="37"/>
-      <c r="D25" s="38"/>
-      <c r="E25" s="38"/>
-      <c r="F25" s="38"/>
-      <c r="G25" s="38"/>
-      <c r="H25" s="38"/>
-      <c r="I25" s="38"/>
-      <c r="J25" s="38"/>
-      <c r="K25" s="38"/>
-      <c r="L25" s="38"/>
-      <c r="M25" s="38"/>
-      <c r="N25" s="38"/>
-      <c r="O25" s="40"/>
+      <c r="C25" s="11"/>
+      <c r="O25" s="29"/>
     </row>
     <row r="26" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="36" t="s">
+      <c r="A26" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="B26" s="37" t="s">
+      <c r="B26" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="C26" s="37"/>
-      <c r="D26" s="38"/>
-      <c r="E26" s="38"/>
-      <c r="F26" s="38"/>
-      <c r="G26" s="38"/>
-      <c r="H26" s="38"/>
-      <c r="I26" s="38"/>
-      <c r="J26" s="38"/>
-      <c r="K26" s="38"/>
-      <c r="L26" s="38"/>
-      <c r="M26" s="38"/>
-      <c r="N26" s="38"/>
-      <c r="O26" s="40"/>
+      <c r="C26" s="11"/>
+      <c r="O26" s="29"/>
     </row>
     <row r="27" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="36" t="s">
+      <c r="A27" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="B27" s="37" t="s">
+      <c r="B27" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="C27" s="37"/>
-      <c r="D27" s="38"/>
-      <c r="E27" s="38"/>
-      <c r="F27" s="38"/>
-      <c r="G27" s="38"/>
-      <c r="H27" s="38"/>
-      <c r="I27" s="38"/>
-      <c r="J27" s="38"/>
-      <c r="K27" s="38"/>
-      <c r="L27" s="38"/>
-      <c r="M27" s="38"/>
-      <c r="N27" s="38"/>
-      <c r="O27" s="40"/>
+      <c r="C27" s="11"/>
+      <c r="O27" s="29"/>
     </row>
     <row r="28" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="36" t="s">
+      <c r="A28" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="B28" s="37" t="s">
+      <c r="B28" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="C28" s="37"/>
-      <c r="D28" s="38"/>
-      <c r="E28" s="38"/>
-      <c r="F28" s="38"/>
-      <c r="G28" s="38"/>
-      <c r="H28" s="38"/>
-      <c r="I28" s="38"/>
-      <c r="J28" s="38"/>
-      <c r="K28" s="38"/>
-      <c r="L28" s="38"/>
-      <c r="M28" s="38"/>
-      <c r="N28" s="38"/>
-      <c r="O28" s="40"/>
+      <c r="C28" s="11"/>
+      <c r="O28" s="29"/>
     </row>
     <row r="29" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="36" t="s">
+      <c r="A29" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="B29" s="37" t="s">
+      <c r="B29" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="C29" s="37"/>
-      <c r="D29" s="38"/>
-      <c r="E29" s="38"/>
-      <c r="F29" s="38"/>
-      <c r="G29" s="38"/>
-      <c r="H29" s="38"/>
-      <c r="I29" s="38"/>
-      <c r="J29" s="38"/>
-      <c r="K29" s="38"/>
-      <c r="L29" s="38"/>
-      <c r="M29" s="38"/>
-      <c r="N29" s="38"/>
-      <c r="O29" s="40"/>
+      <c r="C29" s="11"/>
+      <c r="O29" s="29"/>
     </row>
     <row r="30" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="36" t="s">
+      <c r="A30" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="B30" s="37" t="s">
+      <c r="B30" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="C30" s="37"/>
-      <c r="D30" s="38"/>
-      <c r="E30" s="38"/>
-      <c r="F30" s="38"/>
-      <c r="G30" s="38"/>
-      <c r="H30" s="38"/>
-      <c r="I30" s="38"/>
-      <c r="J30" s="38"/>
-      <c r="K30" s="38"/>
-      <c r="L30" s="38"/>
-      <c r="M30" s="38"/>
-      <c r="N30" s="38"/>
-      <c r="O30" s="40"/>
+      <c r="C30" s="11"/>
+      <c r="O30" s="29"/>
     </row>
     <row r="31" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="36" t="s">
+      <c r="A31" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="B31" s="37" t="s">
+      <c r="B31" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="C31" s="37"/>
-      <c r="D31" s="38"/>
-      <c r="E31" s="38"/>
-      <c r="F31" s="38"/>
-      <c r="G31" s="38"/>
-      <c r="H31" s="38"/>
-      <c r="I31" s="38"/>
-      <c r="J31" s="38"/>
-      <c r="K31" s="38"/>
-      <c r="L31" s="38"/>
-      <c r="M31" s="38"/>
-      <c r="N31" s="38"/>
-      <c r="O31" s="40"/>
+      <c r="C31" s="11"/>
+      <c r="O31" s="29"/>
     </row>
     <row r="32" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="43"/>
-      <c r="B32" s="38"/>
-      <c r="C32" s="38"/>
-      <c r="D32" s="38"/>
-      <c r="E32" s="38"/>
-      <c r="F32" s="38"/>
-      <c r="G32" s="38"/>
-      <c r="H32" s="38"/>
-      <c r="I32" s="38"/>
-      <c r="J32" s="38"/>
-      <c r="K32" s="38"/>
-      <c r="L32" s="38"/>
-      <c r="M32" s="38"/>
-      <c r="N32" s="38"/>
-      <c r="O32" s="40"/>
+      <c r="A32" s="32"/>
+      <c r="O32" s="29"/>
     </row>
     <row r="33" spans="1:15" s="1" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="44"/>
+      <c r="A33" s="33"/>
       <c r="B33" s="12"/>
       <c r="C33" s="12"/>
       <c r="D33" s="13"/>
@@ -5973,7 +5732,7 @@
       <c r="L33" s="13"/>
       <c r="M33" s="13"/>
       <c r="N33" s="13"/>
-      <c r="O33" s="45"/>
+      <c r="O33" s="34"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5990,18 +5749,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="85a5ac57-ba5d-4177-9d0c-591052d7f348">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <Time xmlns="85a5ac57-ba5d-4177-9d0c-591052d7f348" xsi:nil="true"/>
-    <TaxCatchAll xmlns="83eab42e-f602-470e-853a-ac3de8023815" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010006883B3187DBC14A9D90AF7970A68C13" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="4f2ac5f70337d8a6c962a9bd9a156130">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="85a5ac57-ba5d-4177-9d0c-591052d7f348" xmlns:ns3="83eab42e-f602-470e-853a-ac3de8023815" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f375b9bf2fb3ea47ccc5d77caf02b8ee" ns2:_="" ns3:_="">
     <xsd:import namespace="85a5ac57-ba5d-4177-9d0c-591052d7f348"/>
@@ -6248,6 +5995,18 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="85a5ac57-ba5d-4177-9d0c-591052d7f348">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <Time xmlns="85a5ac57-ba5d-4177-9d0c-591052d7f348" xsi:nil="true"/>
+    <TaxCatchAll xmlns="83eab42e-f602-470e-853a-ac3de8023815" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9693287D-49D9-49CC-A36C-9CA2B4702F9C}">
   <ds:schemaRefs>
@@ -6257,17 +6016,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CE5D0A78-3D60-4B03-B08D-DEAD4D5E8E32}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="85a5ac57-ba5d-4177-9d0c-591052d7f348"/>
-    <ds:schemaRef ds:uri="83eab42e-f602-470e-853a-ac3de8023815"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F04EB29F-FE2F-42A4-BC36-6A45D216BF91}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -6284,4 +6032,15 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CE5D0A78-3D60-4B03-B08D-DEAD4D5E8E32}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="85a5ac57-ba5d-4177-9d0c-591052d7f348"/>
+    <ds:schemaRef ds:uri="83eab42e-f602-470e-853a-ac3de8023815"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>